--- a/Outputs/Scenarios/PtX_demand_PL_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PL_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.01032955500440896</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00310974915208654</v>
+        <v>0.003376484447995585</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.005182915253477567</v>
+        <v>0.004892542241271683</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>0.0001488314026094087</v>
       </c>
       <c r="K28" t="n">
-        <v>0.002073166101391027</v>
+        <v>0.002096803817687864</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.01529164859790063</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01678264658449233</v>
+        <v>0.01822215954322981</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02797107764082055</v>
+        <v>0.02640399701688789</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.000804823610415823</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01118843105632822</v>
+        <v>0.01131599872152338</v>
       </c>
     </row>
     <row r="43">
